--- a/assets/source-archive/alpha-v260-xlsx-import/sources/阵法卡列表-共17张卡.xlsx
+++ b/assets/source-archive/alpha-v260-xlsx-import/sources/阵法卡列表-共17张卡.xlsx
@@ -159,7 +159,7 @@
     <t>复合法阵</t>
   </si>
   <si>
-    <t>【基础法阵】+【强化法阵】</t>
+    <t>【基础法阵】+【标准法阵】</t>
   </si>
   <si>
     <t>无效果。</t>
@@ -168,7 +168,7 @@
     <t>增幅法阵</t>
   </si>
   <si>
-    <t>【基础法阵】+【强化法阵】+解析区塑能/咒法派系法术卡×1</t>
+    <t>【复合法阵】+解析区塑能/咒法派系法术卡×1</t>
   </si>
   <si>
     <t>无效果。</t>
@@ -186,7 +186,7 @@
     <t>幻象法阵</t>
   </si>
   <si>
-    <t>【复合法阵】+解析区幻术/惑控派系法术卡×1</t>
+    <t>【基础法阵】+【强化法阵】+解析区幻术/惑控派系法术卡×1</t>
   </si>
   <si>
     <t>无效果。</t>
@@ -214,10 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <charset val="1344"/>
@@ -233,14 +230,9 @@
       <name val="微软雅黑"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b/>
-      <sz val="10"/>
-    </font>
     <font/>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -250,11 +242,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="2F5597"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="EDF2FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -275,43 +262,19 @@
       </bottom>
     </border>
   </borders>
-  <cellXfs count="13">
+  <cellXfs count="5">
     <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="2" borderId="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="3" borderId="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="2" borderId="1" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" applyFont="1">
+    <xf fontId="3" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -384,13 +347,13 @@
       <c r="K2" s="2"/>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="2" t="n">
@@ -408,51 +371,51 @@
       <c r="H3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="2"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="7" t="s">
+      <c r="D4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="7"/>
-      <c r="K4" s="5"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="2" t="n">
@@ -470,51 +433,51 @@
       <c r="H5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="2"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="D6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="5"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="2" t="n">
@@ -532,51 +495,51 @@
       <c r="H7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="2"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" s="5" t="n">
+      <c r="D8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="7" t="s">
+      <c r="H8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="5"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="2" t="n">
@@ -594,72 +557,72 @@
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="4"/>
-      <c r="K9" s="2"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="5" t="n">
+      <c r="E10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="H10" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="7" t="s">
+      <c r="H10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="5"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D12" s="2" t="n">
@@ -677,51 +640,51 @@
       <c r="H12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="2"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="A13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="5" t="n">
+      <c r="D13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="H13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="7" t="s">
+      <c r="H13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="5"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="3" t="n">
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D14" s="2" t="n">
@@ -739,51 +702,51 @@
       <c r="H14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="2"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="5" t="n">
+      <c r="E15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="J15" s="7"/>
-      <c r="K15" s="5"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="3" t="n">
         <v>5</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D16" s="2" t="n">
@@ -801,51 +764,51 @@
       <c r="H16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J16" s="4"/>
-      <c r="K16" s="2"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" s="5" t="n">
+      <c r="D17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H17" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I17" s="7" t="s">
+      <c r="H17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="J17" s="7"/>
-      <c r="K17" s="5"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="3" t="n">
         <v>7</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D18" s="2" t="n">
@@ -863,51 +826,51 @@
       <c r="H18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J18" s="4"/>
-      <c r="K18" s="2"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="12" t="n">
+      <c r="A19" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="5" t="n">
+      <c r="E19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J19" s="7"/>
-      <c r="K19" s="5"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="3" t="n">
         <v>9</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D20" s="2" t="n">
@@ -925,11 +888,11 @@
       <c r="H20" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J20" s="4"/>
-      <c r="K20" s="2"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
     </row>
     <row r="21" ht="15" customHeight="1"/>
     <row r="22" ht="15" customHeight="1"/>
